--- a/public/exports/29189951.xlsx
+++ b/public/exports/29189951.xlsx
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487931</t>
+          <t xml:space="preserve">336193, 336194</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F4">
-        <v>577</v>
+        <v>522</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487931, 100758857</t>
+          <t xml:space="preserve">4487931</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F5">
-        <v>2080</v>
+        <v>577</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490480</t>
+          <t xml:space="preserve">4487931, 100758857</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F6">
-        <v>274</v>
+        <v>2080</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">500078, 500086, 500087, 500088, 500092, 500079, 500080, 500081, 500082, 500083, 500084, 500085, 500089, 500090, 500091, 500093, 100041057</t>
+          <t xml:space="preserve">4490480</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F7">
-        <v>3948</v>
+        <v>274</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5012031</t>
+          <t xml:space="preserve">500078, 500086, 500087, 500088, 500092, 500079, 500080, 500081, 500082, 500083, 500084, 500085, 500089, 500090, 500091, 500093, 100041057</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F8">
-        <v>729</v>
+        <v>3948</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5012485, 100278812</t>
+          <t xml:space="preserve">5012031</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F9">
-        <v>953</v>
+        <v>729</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">741259, 7520400</t>
+          <t xml:space="preserve">741267, 1478906</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>852</v>
+        <v>590</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">741267, 1478906</t>
+          <t xml:space="preserve">741566, 3428403</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F24">
-        <v>590</v>
+        <v>271</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">741566, 3428403</t>
+          <t xml:space="preserve">8659317</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>271</v>
+        <v>527</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8475902</t>
+          <t xml:space="preserve">9704583</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F26">
-        <v>2034</v>
+        <v>1225</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,30 +1331,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8475902</t>
+          <t xml:space="preserve">741259, 7520400</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F27">
-        <v>409</v>
+        <v>852</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047564</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-04-04</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1381,30 +1381,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8659317</t>
+          <t xml:space="preserve">4493354</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F28">
-        <v>527</v>
+        <v>252</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200061035</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-07-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1431,30 +1431,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9704583</t>
+          <t xml:space="preserve">4491116</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F29">
-        <v>1225</v>
+        <v>4480</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311000400</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-05-28</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1481,35 +1481,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493354</t>
+          <t xml:space="preserve">4492286</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30">
-        <v>252</v>
+        <v>4309</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">200061035</t>
+          <t xml:space="preserve">311346092</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-07-31</t>
+          <t xml:space="preserve">2028-11-09</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1531,35 +1531,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4491116</t>
+          <t xml:space="preserve">4493354</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>4480</v>
+        <v>755</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311000400</t>
+          <t xml:space="preserve">311349436</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-28</t>
+          <t xml:space="preserve">2028-11-30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4492286</t>
+          <t xml:space="preserve">9167463</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="F32">
-        <v>4309</v>
+        <v>1097</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346092</t>
+          <t xml:space="preserve">311388713</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-09</t>
+          <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493354</t>
+          <t xml:space="preserve">9167463</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F33">
-        <v>755</v>
+        <v>1097</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349436</t>
+          <t xml:space="preserve">311388713</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-30</t>
+          <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F34">
-        <v>1097</v>
+        <v>1086</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9167463</t>
+          <t xml:space="preserve">5012031</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>1097</v>
+        <v>1806</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311388713</t>
+          <t xml:space="preserve">311390276</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-12</t>
+          <t xml:space="preserve">2029-07-26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9167463</t>
+          <t xml:space="preserve">4490148</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F36">
-        <v>1086</v>
+        <v>1108</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311388713</t>
+          <t xml:space="preserve">311391904</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-12</t>
+          <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5012031</t>
+          <t xml:space="preserve">4490148</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F37">
-        <v>1806</v>
+        <v>3751</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390276</t>
+          <t xml:space="preserve">311391901</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-26</t>
+          <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1886,11 +1886,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F38">
-        <v>1108</v>
+        <v>2706</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1936,15 +1936,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F39">
-        <v>3751</v>
+        <v>1244</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391901</t>
+          <t xml:space="preserve">311391904</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490148</t>
+          <t xml:space="preserve">4487912</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>2706</v>
+        <v>841</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391904</t>
+          <t xml:space="preserve">311392333</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-08</t>
+          <t xml:space="preserve">2029-08-12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490148</t>
+          <t xml:space="preserve">4487931</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>1244</v>
+        <v>3275</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391904</t>
+          <t xml:space="preserve">311393455</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-08</t>
+          <t xml:space="preserve">2029-08-16</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487912</t>
+          <t xml:space="preserve">5729614</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="F42">
-        <v>841</v>
+        <v>7775</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311392333</t>
+          <t xml:space="preserve">311396895</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-12</t>
+          <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487931</t>
+          <t xml:space="preserve">5729614</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F43">
-        <v>3275</v>
+        <v>1216</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393455</t>
+          <t xml:space="preserve">311396890</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-16</t>
+          <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5729614</t>
+          <t xml:space="preserve">9704583</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,16 +2190,16 @@
         </is>
       </c>
       <c r="F44">
-        <v>7775</v>
+        <v>287</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396895</t>
+          <t xml:space="preserve">311403922</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-05</t>
+          <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5729614</t>
+          <t xml:space="preserve">9704583</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F45">
-        <v>1216</v>
+        <v>890</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396890</t>
+          <t xml:space="preserve">311403922</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-05</t>
+          <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F46">
-        <v>287</v>
+        <v>1965</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F47">
-        <v>890</v>
+        <v>1288</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F48">
-        <v>1965</v>
+        <v>979</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2436,20 +2436,20 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F49">
-        <v>1288</v>
+        <v>1933</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403922</t>
+          <t xml:space="preserve">311436781</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-15</t>
+          <t xml:space="preserve">2030-05-07</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9704583</t>
+          <t xml:space="preserve">5731892</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F50">
-        <v>979</v>
+        <v>2212</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403922</t>
+          <t xml:space="preserve">311530550</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-15</t>
+          <t xml:space="preserve">2031-06-23</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9704583</t>
+          <t xml:space="preserve">3427783</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>1933</v>
+        <v>1960</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311436781</t>
+          <t xml:space="preserve">311539266</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-07</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5731892</t>
+          <t xml:space="preserve">3427783</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F52">
-        <v>2212</v>
+        <v>2428</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311530550</t>
+          <t xml:space="preserve">311539266</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-23</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3427783</t>
+          <t xml:space="preserve">7789133</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,16 +2640,16 @@
         </is>
       </c>
       <c r="F53">
-        <v>1960</v>
+        <v>1046</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539266</t>
+          <t xml:space="preserve">311547308</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-05</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3427783</t>
+          <t xml:space="preserve">100025375</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>2428</v>
+        <v>1260</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539266</t>
+          <t xml:space="preserve">311559181</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-05</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7789133</t>
+          <t xml:space="preserve">5012485, 100278812</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F55">
-        <v>1046</v>
+        <v>953</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547308</t>
+          <t xml:space="preserve">311585772</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025375</t>
+          <t xml:space="preserve">8475902</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F56">
-        <v>1260</v>
+        <v>2034</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559181</t>
+          <t xml:space="preserve">311655033</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">336193, 336194</t>
+          <t xml:space="preserve">8475902</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F57">
-        <v>522</v>
+        <v>409</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644701</t>
+          <t xml:space="preserve">311655033</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-24</t>
+          <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">

--- a/public/exports/29189951.xlsx
+++ b/public/exports/29189951.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:L90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gimsinghovedvej 8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100365817</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1476</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1482602</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>2465</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kongevejen 39</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">336193, 336194</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>522</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langhøjvej 29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">4487931</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>577</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">4487931, 100758857</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>2080</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trudsøvej 3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490480</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>274</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Fjorden 2A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">500078, 500086, 500087, 500088, 500092, 500079, 500080, 500081, 500082, 500083, 500084, 500085, 500089, 500090, 500091, 500093, 100041057</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>3948</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Chr Gades Vej 34</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">5012031</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>729</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Voldgade 14E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">5729581</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>1634</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Park Alle 10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">5729614</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>282</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732344</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>505</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732344</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>1457</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gimsinghovedvej 10</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732448</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>1238</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gimsinghovedvej 14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732448</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>3930</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kulgade 4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732783</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>275</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordkajen 4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">741195, 7241308</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>1770</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnevej 25</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">741197, 5732779</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">27</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>1568</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnevej 25</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">741197, 5732779</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>360</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østkajen 2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">741198, 7241308</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>3778</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løvsangervej 2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">741249, 1482602</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>328</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Fjorden 14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">741252, 7520403</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>709</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingvej 1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">741267, 1478906</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>590</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Enghavevej 19B</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">741566, 3428403</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>271</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Godthåbsvej 10</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">8659317</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>527</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rughavevej 5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">9704583</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1225</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Fjorden 25</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">741259, 7520400</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>852</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">200047564</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-04</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7560</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">4493354</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>252</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">200061035</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2022-07-31</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Peter Bangs Vej 15</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">4491116</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>4480</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311000400</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-05-28</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7560</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">4492286</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>4309</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311346092</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-11-09</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7560</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">4493354</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>755</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311349436</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-11-30</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">9167463</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>1097</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311388713</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">9167463</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>1097</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311388713</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">9167463</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>1086</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311388713</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Chr Gades Vej 32</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">5012031</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>1806</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311390276</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-07-26</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drøwten 1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490148</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1108</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311391904</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drøwten 1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490148</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>3751</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311391901</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drøwten 1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490148</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>2706</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311391904</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drøwten 1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490148</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>1244</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311391904</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bækvej 6</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">4487912</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>841</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311392333</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-12</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langhøjvej 29</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">4487931</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>3275</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311393455</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-16</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Park Alle 2</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">5729614</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>7775</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311396895</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Park Alle 2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">5729614</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>1216</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311396890</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 8</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">9704583</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>287</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311403922</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 8</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">9704583</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>890</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311403922</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 8</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">9704583</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>1965</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311403922</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 8</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">9704583</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>1288</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311403922</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 8</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">9704583</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>979</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311403922</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rughavevej 5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">9704583</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>1933</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311436781</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-05-07</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedegade 1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731892</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>2212</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311530550</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-23</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rolighedsvej 1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">3427783</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>1960</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311539266</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rolighedsvej 1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">3427783</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>2428</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311539266</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bremdal Torv 2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">7789133</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>1046</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311547308</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rughavevej 18</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">100025375</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>1260</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311559181</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fjordvejen 10B</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">5012485, 100278812</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>953</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311585772</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Morten Andersens Passage 5</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">8475902</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>2034</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311655033</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Morten Andersens Passage 5</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">8475902</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>409</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311655033</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 13</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732344</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>1287</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311758709</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-13</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Peter Bangs Vej 15</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">4491116</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>2759</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311763744</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Peter Bangs Vej 15</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">4491116</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>3292</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311763744</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gimsinghovedvej 13</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731864</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>1069</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311764270</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-05</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Peter Bangs Vej 15</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">4491116</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>2436</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311764960</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-07</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ølbyvej 43</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">5729509</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>445</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311768244</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-21</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tegltorvet 2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">5730029</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>1323</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311771862</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-07-06</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gimsinghoved 1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490214</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>733</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311774489</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-07-22</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Park Alle 14</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731244</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>826</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311782512</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-09-04</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sønderlandsgade 5</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7790</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">3428644</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>569</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311784615</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-09-13</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Farvervej 3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">100006226</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>1788</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311791535</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Fjorden 8</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">741272, 7520401</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>372</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311795845</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-06</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 3</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7560</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">4493313</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>397</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311800349</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bredgade 6</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731910</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>1103</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311800350</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Park Alle 16</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">8560785</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>1883</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311838191</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-15</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Voldgade 67</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">5729561</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>3635</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311844320</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Voldgade 14</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">5729581</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>5796</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311864040</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-23</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drøwten 6</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490517</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>1153</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311865379</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fjordvejen 28</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">9936805</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>2692</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311867611</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bjerggade 52</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732138</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>768</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311875083</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-05</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bjerggade 54</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732138</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>691</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311875083</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-05</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bjerggade 50</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">5732138</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>742</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311875083</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-05</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trudsøvej 3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490480</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>597</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311875794</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trudsøvej 5</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490480</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>799</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311876218</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-12</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trudsøvej 5</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">4490480</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>1197</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311876218</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-12</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 5A</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731937</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>866</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311901053</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-13</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 5</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731937</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>1696</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311902800</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 5</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731937</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>2556</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311902800</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 5</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731937</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>659</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311902800</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 5</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">5731937</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>431</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311902800</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnevej 6</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">9755992, 100210899</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>824</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311904611</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-29</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Anlægsvej 8</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">5730476</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>2034</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311920933</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-08-22</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,39 +5371,49 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Anlægsvej 6</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7600</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">5730476</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>4373</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311920933</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-08-22</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J90"/>
+  <autoFilter ref="A1:L90"/>
 </worksheet>
 </file>
--- a/public/exports/29189951.xlsx
+++ b/public/exports/29189951.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gimsinghovedvej 8</t>
+          <t xml:space="preserve">Bækvej 2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100365817</t>
+          <t xml:space="preserve">4487931, 100758857</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H2">
-        <v>1476</v>
+        <v>2080</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 1</t>
+          <t xml:space="preserve">Chr Gades Vej 34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1482602</t>
+          <t xml:space="preserve">5012031</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H3">
-        <v>2465</v>
+        <v>729</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,17 +211,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 39</t>
+          <t xml:space="preserve">Drosselvej 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7790</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">336193, 336194</t>
+          <t xml:space="preserve">1482602</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,7 +230,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>522</v>
+        <v>2465</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,17 +271,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langhøjvej 29</t>
+          <t xml:space="preserve">Enghavevej 19B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7790</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487931</t>
+          <t xml:space="preserve">741566, 3428403</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="H5">
-        <v>577</v>
+        <v>271</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 2</t>
+          <t xml:space="preserve">Gimsinghovedvej 10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487931, 100758857</t>
+          <t xml:space="preserve">5732448</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H6">
-        <v>2080</v>
+        <v>1238</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trudsøvej 3</t>
+          <t xml:space="preserve">Gimsinghovedvej 14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490480</t>
+          <t xml:space="preserve">5732448</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H7">
-        <v>274</v>
+        <v>3930</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 2A</t>
+          <t xml:space="preserve">Gimsinghovedvej 8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">500078, 500086, 500087, 500088, 500092, 500079, 500080, 500081, 500082, 500083, 500084, 500085, 500089, 500090, 500091, 500093, 100041057</t>
+          <t xml:space="preserve">100365817</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H8">
-        <v>3948</v>
+        <v>1476</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chr Gades Vej 34</t>
+          <t xml:space="preserve">Godthåbsvej 10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5012031</t>
+          <t xml:space="preserve">8659317</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H9">
-        <v>729</v>
+        <v>527</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Voldgade 14E</t>
+          <t xml:space="preserve">Havnevej 25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5729581</t>
+          <t xml:space="preserve">741197, 5732779</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="H10">
-        <v>1634</v>
+        <v>1568</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Park Alle 10</t>
+          <t xml:space="preserve">Havnevej 25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5729614</t>
+          <t xml:space="preserve">741197, 5732779</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="H11">
-        <v>282</v>
+        <v>360</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 13</t>
+          <t xml:space="preserve">Kulgade 4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5732344</t>
+          <t xml:space="preserve">5732783</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>505</v>
+        <v>275</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 13</t>
+          <t xml:space="preserve">Langhøjvej 29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5732344</t>
+          <t xml:space="preserve">4487931</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H13">
-        <v>1457</v>
+        <v>577</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gimsinghovedvej 10</t>
+          <t xml:space="preserve">Løvsangervej 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5732448</t>
+          <t xml:space="preserve">741249, 1482602</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="H14">
-        <v>1238</v>
+        <v>328</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gimsinghovedvej 14</t>
+          <t xml:space="preserve">Nordkajen 4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5732448</t>
+          <t xml:space="preserve">741195, 7241308</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H15">
-        <v>3930</v>
+        <v>1770</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulgade 4</t>
+          <t xml:space="preserve">Park Alle 10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5732783</t>
+          <t xml:space="preserve">5729614</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H16">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordkajen 4</t>
+          <t xml:space="preserve">Rughavevej 5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7790</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">741195, 7241308</t>
+          <t xml:space="preserve">9704583</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H17">
-        <v>1770</v>
+        <v>1225</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 25</t>
+          <t xml:space="preserve">Tingvej 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">741197, 5732779</t>
+          <t xml:space="preserve">741267, 1478906</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H18">
-        <v>1568</v>
+        <v>590</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 25</t>
+          <t xml:space="preserve">Trudsøvej 3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">741197, 5732779</t>
+          <t xml:space="preserve">4490480</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H19">
-        <v>360</v>
+        <v>274</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østkajen 2</t>
+          <t xml:space="preserve">Ved Fjorden 14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">741198, 7241308</t>
+          <t xml:space="preserve">741252, 7520403</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H20">
-        <v>3778</v>
+        <v>709</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løvsangervej 2</t>
+          <t xml:space="preserve">Ved Fjorden 2A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">741249, 1482602</t>
+          <t xml:space="preserve">500078, 500086, 500087, 500088, 500092, 500079, 500080, 500081, 500082, 500083, 500084, 500085, 500089, 500090, 500091, 500093, 100041057</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H21">
-        <v>328</v>
+        <v>3948</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 14</t>
+          <t xml:space="preserve">Voldgade 14E</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">741252, 7520403</t>
+          <t xml:space="preserve">5729581</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H22">
-        <v>709</v>
+        <v>1634</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 1</t>
+          <t xml:space="preserve">Østergade 13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">741267, 1478906</t>
+          <t xml:space="preserve">5732344</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H23">
-        <v>590</v>
+        <v>505</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 19B</t>
+          <t xml:space="preserve">Østergade 13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7790</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">741566, 3428403</t>
+          <t xml:space="preserve">5732344</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H24">
-        <v>271</v>
+        <v>1457</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 10</t>
+          <t xml:space="preserve">Østkajen 2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8659317</t>
+          <t xml:space="preserve">741198, 7241308</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H25">
-        <v>527</v>
+        <v>3778</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,40 +1531,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rughavevej 5</t>
+          <t xml:space="preserve">Ved Fjorden 25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7790</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9704583</t>
+          <t xml:space="preserve">741259, 7520400</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H26">
-        <v>1225</v>
+        <v>852</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047564</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-04-04</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1591,35 +1591,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 25</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7560</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">741259, 7520400</t>
+          <t xml:space="preserve">4493354</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H27">
-        <v>852</v>
+        <v>252</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047564</t>
+          <t xml:space="preserve">200061035</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-04</t>
+          <t xml:space="preserve">2022-07-31</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,35 +1651,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Peter Bangs Vej 15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7560</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493354</t>
+          <t xml:space="preserve">4491116</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>252</v>
+        <v>4480</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">200061035</t>
+          <t xml:space="preserve">311000400</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-07-31</t>
+          <t xml:space="preserve">2023-05-28</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,45 +1711,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Bangs Vej 15</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7560</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4491116</t>
+          <t xml:space="preserve">4492286</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>4480</v>
+        <v>4309</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311000400</t>
+          <t xml:space="preserve">311346092</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-28</t>
+          <t xml:space="preserve">2028-11-09</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4492286</t>
+          <t xml:space="preserve">4493354</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>4309</v>
+        <v>755</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346092</t>
+          <t xml:space="preserve">311349436</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-09</t>
+          <t xml:space="preserve">2028-11-30</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Drosselvej 5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7560</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493354</t>
+          <t xml:space="preserve">9167463</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="H31">
-        <v>755</v>
+        <v>1097</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349436</t>
+          <t xml:space="preserve">311388713</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-30</t>
+          <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H32">
@@ -1966,11 +1966,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H33">
-        <v>1097</v>
+        <v>1086</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 5</t>
+          <t xml:space="preserve">Chr Gades Vej 32</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,25 +2021,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9167463</t>
+          <t xml:space="preserve">5012031</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>1086</v>
+        <v>1806</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311388713</t>
+          <t xml:space="preserve">311390276</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-12</t>
+          <t xml:space="preserve">2029-07-26</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chr Gades Vej 32</t>
+          <t xml:space="preserve">Drøwten 1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5012031</t>
+          <t xml:space="preserve">4490148</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H35">
-        <v>1806</v>
+        <v>1108</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390276</t>
+          <t xml:space="preserve">311391904</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-26</t>
+          <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2146,15 +2146,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H36">
-        <v>1108</v>
+        <v>3751</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391904</t>
+          <t xml:space="preserve">311391901</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2206,15 +2206,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H37">
-        <v>3751</v>
+        <v>2706</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391901</t>
+          <t xml:space="preserve">311391904</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2266,11 +2266,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H38">
-        <v>2706</v>
+        <v>1244</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drøwten 1</t>
+          <t xml:space="preserve">Bækvej 6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,25 +2321,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490148</t>
+          <t xml:space="preserve">4487912</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>1244</v>
+        <v>841</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391904</t>
+          <t xml:space="preserve">311392333</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-08</t>
+          <t xml:space="preserve">2029-08-12</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækvej 6</t>
+          <t xml:space="preserve">Langhøjvej 29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487912</t>
+          <t xml:space="preserve">4487931</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="H40">
-        <v>841</v>
+        <v>3275</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311392333</t>
+          <t xml:space="preserve">311393455</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-12</t>
+          <t xml:space="preserve">2029-08-16</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langhøjvej 29</t>
+          <t xml:space="preserve">Park Alle 2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487931</t>
+          <t xml:space="preserve">5729614</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,16 +2450,16 @@
         </is>
       </c>
       <c r="H41">
-        <v>3275</v>
+        <v>7775</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393455</t>
+          <t xml:space="preserve">311396895</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-16</t>
+          <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2506,15 +2506,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H42">
-        <v>7775</v>
+        <v>1216</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396895</t>
+          <t xml:space="preserve">311396890</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Park Alle 2</t>
+          <t xml:space="preserve">Skolegade 8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7790</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5729614</t>
+          <t xml:space="preserve">9704583</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>1216</v>
+        <v>287</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396890</t>
+          <t xml:space="preserve">311403922</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-05</t>
+          <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2626,11 +2626,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H44">
-        <v>287</v>
+        <v>890</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2686,11 +2686,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H45">
-        <v>890</v>
+        <v>1965</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2746,11 +2746,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H46">
-        <v>1965</v>
+        <v>1288</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2806,11 +2806,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H47">
-        <v>1288</v>
+        <v>979</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 8</t>
+          <t xml:space="preserve">Rughavevej 5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2866,20 +2866,20 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H48">
-        <v>979</v>
+        <v>1933</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403922</t>
+          <t xml:space="preserve">311436781</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-15</t>
+          <t xml:space="preserve">2030-05-07</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,35 +2911,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rughavevej 5</t>
+          <t xml:space="preserve">Smedegade 1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7790</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9704583</t>
+          <t xml:space="preserve">5731892</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>1933</v>
+        <v>2212</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311436781</t>
+          <t xml:space="preserve">311530550</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-07</t>
+          <t xml:space="preserve">2031-06-23</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 1</t>
+          <t xml:space="preserve">Rolighedsvej 1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7790</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5731892</t>
+          <t xml:space="preserve">3427783</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="H50">
-        <v>2212</v>
+        <v>1960</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311530550</t>
+          <t xml:space="preserve">311539266</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-23</t>
+          <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3046,11 +3046,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H51">
-        <v>1960</v>
+        <v>2428</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,35 +3091,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 1</t>
+          <t xml:space="preserve">Bremdal Torv 2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7790</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3427783</t>
+          <t xml:space="preserve">7789133</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H52">
-        <v>2428</v>
+        <v>1046</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539266</t>
+          <t xml:space="preserve">311547308</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-05</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bremdal Torv 2</t>
+          <t xml:space="preserve">Rughavevej 18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7790</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7789133</t>
+          <t xml:space="preserve">100025375</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,16 +3170,16 @@
         </is>
       </c>
       <c r="H53">
-        <v>1046</v>
+        <v>1260</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547308</t>
+          <t xml:space="preserve">311559181</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,35 +3211,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rughavevej 18</t>
+          <t xml:space="preserve">Fjordvejen 10B</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7790</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025375</t>
+          <t xml:space="preserve">5012485, 100278812</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H54">
-        <v>1260</v>
+        <v>953</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559181</t>
+          <t xml:space="preserve">311585772</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,35 +3271,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordvejen 10B</t>
+          <t xml:space="preserve">Kongevejen 39</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7790</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5012485, 100278812</t>
+          <t xml:space="preserve">336193, 336194</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>953</v>
+        <v>522</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585772</t>
+          <t xml:space="preserve">311644701</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-16</t>
+          <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 3</t>
+          <t xml:space="preserve">Bredgade 6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7560</t>
+          <t xml:space="preserve">7600</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4493313</t>
+          <t xml:space="preserve">5731910</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,11 +4190,11 @@
         </is>
       </c>
       <c r="H70">
-        <v>397</v>
+        <v>1103</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800349</t>
+          <t xml:space="preserve">311800350</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 6</t>
+          <t xml:space="preserve">Engvej 3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7600</t>
+          <t xml:space="preserve">7560</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5731910</t>
+          <t xml:space="preserve">4493313</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,11 +4250,11 @@
         </is>
       </c>
       <c r="H71">
-        <v>1103</v>
+        <v>397</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800350</t>
+          <t xml:space="preserve">311800349</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 52</t>
+          <t xml:space="preserve">Bjerggade 50</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4606,11 +4606,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H77">
-        <v>768</v>
+        <v>742</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 54</t>
+          <t xml:space="preserve">Bjerggade 52</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4666,11 +4666,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H78">
-        <v>691</v>
+        <v>768</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 50</t>
+          <t xml:space="preserve">Bjerggade 54</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H79">
-        <v>742</v>
+        <v>691</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsvej 8</t>
+          <t xml:space="preserve">Anlægsvej 6</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5326,11 +5326,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H89">
-        <v>2034</v>
+        <v>4373</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsvej 6</t>
+          <t xml:space="preserve">Anlægsvej 8</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5386,11 +5386,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H90">
-        <v>4373</v>
+        <v>2034</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>

--- a/public/exports/29189951.xlsx
+++ b/public/exports/29189951.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:M90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-04</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-07-31</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kuben Management A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-05-28</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-09</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-30</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-12</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-26</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-12</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-16</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-09-05</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-15</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-07</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-23</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-05</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-13</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-05</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-07</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-21</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-06</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-22</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-04</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-13</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech Solutions A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-06</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-29</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-15</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-23</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4614,20 +4994,25 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875083</t>
+          <t xml:space="preserve">311875195</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-05</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4674,20 +5059,25 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875083</t>
+          <t xml:space="preserve">311875195</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-05</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4734,20 +5124,25 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875083</t>
+          <t xml:space="preserve">311875195</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-05</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-12</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-12</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-13</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-29</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-22</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,21 +5844,26 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-22</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L90"/>
+  <autoFilter ref="A1:M90"/>
 </worksheet>
 </file>
--- a/public/exports/29189951.xlsx
+++ b/public/exports/29189951.xlsx
@@ -4994,7 +4994,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875195</t>
+          <t xml:space="preserve">311875083</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875195</t>
+          <t xml:space="preserve">311875083</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875195</t>
+          <t xml:space="preserve">311875083</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
